--- a/docs/excel/Definición del contrato de la API.xlsx
+++ b/docs/excel/Definición del contrato de la API.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar.lasso-m\Downloads\DOSW_ParcialT2_JoseMartinez\docs\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118CB781-43CA-4626-8D26-0812788B690C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -228,32 +237,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
     </font>
@@ -263,7 +272,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -273,7 +282,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
@@ -287,40 +302,44 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -328,7 +347,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -518,29 +537,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="18.13"/>
-    <col customWidth="1" min="3" max="3" width="28.63"/>
-    <col customWidth="1" min="4" max="4" width="20.13"/>
-    <col customWidth="1" min="5" max="5" width="16.25"/>
-    <col customWidth="1" min="6" max="6" width="41.63"/>
-    <col customWidth="1" min="7" max="7" width="29.63"/>
-    <col customWidth="1" min="8" max="8" width="24.0"/>
-    <col customWidth="1" min="9" max="9" width="27.0"/>
-    <col customWidth="1" min="10" max="10" width="25.0"/>
-    <col customWidth="1" min="11" max="11" width="39.38"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="29.5703125" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="39.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -573,7 +595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -606,7 +628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" ht="180" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -639,7 +661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>29</v>
@@ -672,7 +694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
         <v>38</v>
@@ -705,7 +727,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>44</v>
@@ -738,7 +760,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
@@ -751,7 +773,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
@@ -764,7 +786,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
@@ -777,7 +799,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -791,7 +813,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -804,7 +826,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -825,7 +847,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -846,7 +868,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -867,7 +889,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -888,7 +910,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -909,7 +931,7 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -930,7 +952,7 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -951,7 +973,7 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -972,7 +994,7 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -993,7 +1015,7 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1014,7 +1036,7 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1035,7 +1057,7 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1056,7 +1078,7 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1077,7 +1099,7 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1098,7 +1120,7 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1119,7 +1141,7 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1140,7 +1162,7 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1161,7 +1183,7 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1182,7 +1204,7 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1203,7 +1225,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1224,7 +1246,7 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1245,7 +1267,7 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1266,7 +1288,7 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -1287,7 +1309,7 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="5"/>
       <c r="C35" s="1"/>
@@ -1300,7 +1322,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1313,7 +1335,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1326,7 +1348,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1339,7 +1361,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1352,7 +1374,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1365,10 +1387,10 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B41" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/excel/Definición del contrato de la API.xlsx
+++ b/docs/excel/Definición del contrato de la API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar.lasso-m\Downloads\DOSW_ParcialT2_JoseMartinez\docs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118CB781-43CA-4626-8D26-0812788B690C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6AEA9F-F2DB-4DC9-A69A-1068B1C1D3B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
   <si>
     <t>Caso de Uso</t>
   </si>
@@ -233,16 +233,140 @@
  {"token": "eyJhbG...", "rol": "ADMIN"}
  Errores: 401</t>
   </si>
+  <si>
+    <t>Orden de Validación</t>
+  </si>
+  <si>
+    <t>Escenario de Error</t>
+  </si>
+  <si>
+    <t>Código HTTP</t>
+  </si>
+  <si>
+    <t>Ejemplo de Respuesta JSON de Error</t>
+  </si>
+  <si>
+    <t>1. Disponibilidad de franja</t>
+  </si>
+  <si>
+    <t>E01 - Franja llena</t>
+  </si>
+  <si>
+    <t>409 Conflict</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E01",
+  "mensaje": "Franja llena. Cuarta reserva en la misma fecha y hora.",
+  "estado": 409
+}</t>
+  </si>
+  <si>
+    <t>2. Barbero disponible</t>
+  </si>
+  <si>
+    <t>E100 - Barbero no Disponible</t>
+  </si>
+  <si>
+    <t>422 Unprocessable Entity</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E100",
+  "mensaje": "Ningún barbero con la especialidad requerida está libre en esa franja.",
+  "estado": 422
+}</t>
+  </si>
+  <si>
+    <t>E02 - Especialidad incompatible</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E02",
+  "mensaje": "El barbero seleccionado está libre, pero no tiene la especialidad necesaria para alguno de los servicios solicitados.",
+  "estado": 422
+}</t>
+  </si>
+  <si>
+    <t>3. Datos del cliente</t>
+  </si>
+  <si>
+    <t>E03 - Nombre inválido</t>
+  </si>
+  <si>
+    <t>400 Bad Request</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E03",
+  "mensaje": "El nombre es nulo, vacío o contiene únicamente espacios.",
+  "estado": 400
+}</t>
+  </si>
+  <si>
+    <t>E07 - Teléfono inválido</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E07",
+  "mensaje": "El teléfono es nulo o no contiene exactamente 10 dígitos numéricos.",
+  "estado": 400
+}</t>
+  </si>
+  <si>
+    <t>E08 - Correo inválido</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E08",
+  "mensaje": "El correo es nulo, tiene formato inválido o su dominio es diferente de gmail.com.",
+  "estado": 400
+}</t>
+  </si>
+  <si>
+    <t>4. Servicio permitido</t>
+  </si>
+  <si>
+    <t>E09 - Servicio inexistente</t>
+  </si>
+  <si>
+    <t>404 Not Found</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E09",
+  "mensaje": "Se solicita un identificador de servicio que no existe en el catálogo.",
+  "estado": 404
+}</t>
+  </si>
+  <si>
+    <t>{
+  "codigo": "E01",
+  "mensaje": "Franja llena. Cuarta reserva en la misma fecha y hora.",
+  "estado": 409
+}, {
+  "codigo": "E02",
+  "mensaje": "El barbero seleccionado está libre, pero no tiene la especialidad necesaria para alguno de los servicios solicitados.",
+  "estado": 422
+}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,8 +390,21 @@
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,7 +413,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
@@ -305,29 +448,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -560,283 +711,387 @@
     <col min="9" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
     <col min="11" max="11" width="39.42578125" customWidth="1"/>
+    <col min="12" max="12" width="47.85546875" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="180" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="105" x14ac:dyDescent="0.2">
+      <c r="L3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>37</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" ht="90" x14ac:dyDescent="0.2">
+      <c r="M5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="120" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="M6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="135" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="120" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="M8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -847,17 +1102,17 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -868,17 +1123,17 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -889,17 +1144,17 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -910,17 +1165,17 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -931,17 +1186,17 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -952,17 +1207,17 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -973,17 +1228,17 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -994,17 +1249,17 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1015,17 +1270,17 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1036,17 +1291,17 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1057,17 +1312,17 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1078,17 +1333,17 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1099,17 +1354,17 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1120,17 +1375,17 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1141,17 +1396,17 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -1162,17 +1417,17 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1183,17 +1438,17 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -1204,17 +1459,17 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1225,17 +1480,17 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -1246,17 +1501,17 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -1267,17 +1522,17 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -1288,17 +1543,17 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -1309,9 +1564,9 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="5"/>
+      <c r="B35" s="4"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1322,7 +1577,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1335,7 +1590,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1348,7 +1603,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1361,7 +1616,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1374,7 +1629,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1387,7 +1642,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B41" s="1"/>
     </row>
   </sheetData>

--- a/docs/excel/Definición del contrato de la API.xlsx
+++ b/docs/excel/Definición del contrato de la API.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar.lasso-m\Downloads\DOSW_ParcialT2_JoseMartinez\docs\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d5b8fa97bd6ecd7/Escritorio/DOSW/Parcial/DOSW_ParcialT2_JoseMartinez/docs/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6AEA9F-F2DB-4DC9-A69A-1068B1C1D3B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{ED6AEA9F-F2DB-4DC9-A69A-1068B1C1D3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C79DECC-8CA1-4B6B-A6F0-5962733D7B29}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Caso de Uso</t>
   </si>
@@ -234,120 +239,82 @@
  Errores: 401</t>
   </si>
   <si>
-    <t>Orden de Validación</t>
-  </si>
-  <si>
-    <t>Escenario de Error</t>
-  </si>
-  <si>
-    <t>Código HTTP</t>
-  </si>
-  <si>
-    <t>Ejemplo de Respuesta JSON de Error</t>
-  </si>
-  <si>
-    <t>1. Disponibilidad de franja</t>
-  </si>
-  <si>
-    <t>E01 - Franja llena</t>
-  </si>
-  <si>
-    <t>409 Conflict</t>
-  </si>
-  <si>
-    <t>{
+    <t>Ejemplos de respuesta JSON de Error por Código HTTP</t>
+  </si>
+  <si>
+    <t>Ejemplo 400 (Bad Request):
+{
+  "codigo": "E_FORMATO_FECHA",
+  "mensaje": "La fecha debe tener un formato válido y ser futura.",
+  "estado": 400
+}
+Ejemplo 409 (Conflict):
+{
+  "codigo": "E_TURNO_DUPLICADO",
+  "mensaje": "No se duplica barbero + fecha + hora.",
+  "estado": 409
+}</t>
+  </si>
+  <si>
+    <t>Ejemplo 400 (E03 - Bad Request):
+{
+  "codigo": "E03",
+  "mensaje": "El nombre es nulo, vacío o contiene únicamente espacios.",
+  "estado": 400
+}
+Ejemplo 404 (E09 - Not Found):
+{
+  "codigo": "E09",
+  "mensaje": "Se solicita un identificador de servicio que no existe en el catálogo.",
+  "estado": 404
+}
+Ejemplo 409 (E01 - Conflict):
+{
   "codigo": "E01",
   "mensaje": "Franja llena. Cuarta reserva en la misma fecha y hora.",
   "estado": 409
-}</t>
-  </si>
-  <si>
-    <t>2. Barbero disponible</t>
-  </si>
-  <si>
-    <t>E100 - Barbero no Disponible</t>
-  </si>
-  <si>
-    <t>422 Unprocessable Entity</t>
-  </si>
-  <si>
-    <t>{
-  "codigo": "E100",
-  "mensaje": "Ningún barbero con la especialidad requerida está libre en esa franja.",
-  "estado": 422
-}</t>
-  </si>
-  <si>
-    <t>E02 - Especialidad incompatible</t>
-  </si>
-  <si>
-    <t>{
+}
+Ejemplo 422 (E02 - Unprocessable Entity):
+{
   "codigo": "E02",
   "mensaje": "El barbero seleccionado está libre, pero no tiene la especialidad necesaria para alguno de los servicios solicitados.",
   "estado": 422
 }</t>
   </si>
   <si>
-    <t>3. Datos del cliente</t>
-  </si>
-  <si>
-    <t>E03 - Nombre inválido</t>
-  </si>
-  <si>
-    <t>400 Bad Request</t>
-  </si>
-  <si>
-    <t>{
-  "codigo": "E03",
-  "mensaje": "El nombre es nulo, vacío o contiene únicamente espacios.",
-  "estado": 400
+    <t>Ejemplo 401 (Unauthorized):
+{
+  "codigo": "E_NO_AUTORIZADO",
+  "mensaje": "Token de sesión ausente, inválido o expirado.",
+  "estado": 401
+}
+Ejemplo 403 (Forbidden):
+{
+  "codigo": "E_ACCESO_DENEGADO",
+  "mensaje": "Rol de usuario no tiene permisos para esta acción (Se requiere rol CLIENTE).",
+  "estado": 403
 }</t>
   </si>
   <si>
-    <t>E07 - Teléfono inválido</t>
-  </si>
-  <si>
-    <t>{
-  "codigo": "E07",
-  "mensaje": "El teléfono es nulo o no contiene exactamente 10 dígitos numéricos.",
-  "estado": 400
+    <t>Ejemplo 401 (Unauthorized):
+{
+  "codigo": "E_NO_AUTORIZADO",
+  "mensaje": "Token de sesión ausente, inválido o expirado.",
+  "estado": 401
+}
+Ejemplo 403 (Forbidden):
+{
+  "codigo": "E_ACCESO_DENEGADO",
+  "mensaje": "Rol de usuario no tiene permisos para esta acción (Se requiere rol ADMIN).",
+  "estado": 403
 }</t>
   </si>
   <si>
-    <t>E08 - Correo inválido</t>
-  </si>
-  <si>
-    <t>{
-  "codigo": "E08",
-  "mensaje": "El correo es nulo, tiene formato inválido o su dominio es diferente de gmail.com.",
-  "estado": 400
-}</t>
-  </si>
-  <si>
-    <t>4. Servicio permitido</t>
-  </si>
-  <si>
-    <t>E09 - Servicio inexistente</t>
-  </si>
-  <si>
-    <t>404 Not Found</t>
-  </si>
-  <si>
-    <t>{
-  "codigo": "E09",
-  "mensaje": "Se solicita un identificador de servicio que no existe en el catálogo.",
-  "estado": 404
-}</t>
-  </si>
-  <si>
-    <t>{
-  "codigo": "E01",
-  "mensaje": "Franja llena. Cuarta reserva en la misma fecha y hora.",
-  "estado": 409
-}, {
-  "codigo": "E02",
-  "mensaje": "El barbero seleccionado está libre, pero no tiene la especialidad necesaria para alguno de los servicios solicitados.",
-  "estado": 422
+    <t>Ejemplo 401 (Unauthorized):
+{
+  "codigo": "E_CREDENCIALES_INVALIDAS",
+  "mensaje": "Correo o contraseña incorrectos.",
+  "estado": 401
 }</t>
   </si>
 </sst>
@@ -355,11 +322,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -375,17 +349,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
@@ -398,10 +361,30 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -413,14 +396,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="-0.499984740745262"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -448,37 +431,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{9DD2F503-B5AE-4297-A5AE-6BA210172074}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -699,26 +690,26 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S41"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="41.5703125" customWidth="1"/>
-    <col min="7" max="7" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="41.5546875" customWidth="1"/>
+    <col min="7" max="7" width="29.5546875" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
-    <col min="11" max="11" width="39.42578125" customWidth="1"/>
-    <col min="12" max="12" width="47.85546875" customWidth="1"/>
-    <col min="13" max="13" width="22.85546875" customWidth="1"/>
-    <col min="14" max="14" width="21.28515625" customWidth="1"/>
-    <col min="15" max="15" width="25.5703125" customWidth="1"/>
-    <col min="16" max="16" width="26.42578125" customWidth="1"/>
+    <col min="11" max="11" width="43.33203125" customWidth="1"/>
+    <col min="12" max="12" width="93.21875" customWidth="1"/>
+    <col min="13" max="13" width="22.88671875" customWidth="1"/>
+    <col min="14" max="14" width="31.44140625" customWidth="1"/>
+    <col min="15" max="15" width="39.5546875" customWidth="1"/>
+    <col min="16" max="16" width="53.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="42" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -750,348 +741,299 @@
       <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+    </row>
+    <row r="2" spans="1:19" ht="265.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" ht="285.60000000000002" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="105" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:19" ht="285.60000000000002" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="1:19" ht="168" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="2" t="s">
+      <c r="E6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="180" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="150" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="120" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="135" x14ac:dyDescent="0.2">
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="M7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="120" x14ac:dyDescent="0.2">
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="M8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1102,17 +1044,17 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1123,17 +1065,17 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1144,17 +1086,17 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1165,17 +1107,17 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1186,17 +1128,17 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1207,17 +1149,17 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1228,17 +1170,17 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1249,17 +1191,17 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1270,17 +1212,17 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1291,17 +1233,17 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1312,17 +1254,17 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1333,17 +1275,17 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1354,17 +1296,17 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1375,17 +1317,17 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1396,17 +1338,17 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -1417,17 +1359,17 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1438,17 +1380,17 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -1459,17 +1401,17 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1480,17 +1422,17 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -1501,17 +1443,17 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -1522,17 +1464,17 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -1543,17 +1485,17 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -1564,9 +1506,9 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="4"/>
+      <c r="B35" s="3"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1577,7 +1519,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1590,7 +1532,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1603,7 +1545,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1616,7 +1558,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1629,7 +1571,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1642,7 +1584,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
     </row>
   </sheetData>
